--- a/docs/seep/files/xslope_earth_dam2.xlsx
+++ b/docs/seep/files/xslope_earth_dam2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/njones/python_projects/xslope/docs/seep/files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E733D208-B5E8-2E44-A453-D4E643498B67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0B9B760-0782-FB42-A3A9-F066BF4813D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="30140" yWindow="3620" windowWidth="34200" windowHeight="20240" xr2:uid="{BA54C293-CE08-6E4C-9212-B3317DAA148E}"/>
   </bookViews>
@@ -1062,13 +1062,13 @@
     <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="15" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1093,7 +1093,28 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="7">
+  <dxfs count="10">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="1" tint="0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="1" tint="0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="1" tint="0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -10252,37 +10273,37 @@
     <mergeCell ref="R7:V7"/>
   </mergeCells>
   <conditionalFormatting sqref="E9:F50">
-    <cfRule type="expression" dxfId="6" priority="4">
+    <cfRule type="expression" dxfId="9" priority="4">
       <formula>$D9="cp"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G9:H50">
-    <cfRule type="expression" dxfId="5" priority="3">
+    <cfRule type="expression" dxfId="8" priority="3">
       <formula>$D9="mc"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I9:J50">
-    <cfRule type="expression" dxfId="4" priority="5">
+    <cfRule type="expression" dxfId="7" priority="5">
       <formula>$D9="cp"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M9:N50">
-    <cfRule type="expression" dxfId="3" priority="7">
+    <cfRule type="expression" dxfId="6" priority="7">
       <formula>$D9="cp"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O9:O50">
-    <cfRule type="expression" dxfId="2" priority="14">
+    <cfRule type="expression" dxfId="5" priority="14">
       <formula>$D9="mc"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P9:Q50">
-    <cfRule type="expression" dxfId="1" priority="9">
+    <cfRule type="expression" dxfId="4" priority="9">
       <formula>$D9="cp"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R9:V11">
-    <cfRule type="expression" dxfId="0" priority="1">
+    <cfRule type="expression" dxfId="3" priority="1">
       <formula>$D9="cp"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10336,74 +10357,74 @@
       </c>
     </row>
     <row r="4" spans="1:44" x14ac:dyDescent="0.2">
-      <c r="A4" s="48" t="s">
+      <c r="A4" s="46" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="48"/>
-      <c r="D4" s="48" t="s">
+      <c r="B4" s="46"/>
+      <c r="D4" s="46" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="48"/>
-      <c r="G4" s="48" t="s">
+      <c r="E4" s="46"/>
+      <c r="G4" s="46" t="s">
         <v>6</v>
       </c>
-      <c r="H4" s="48"/>
-      <c r="J4" s="48" t="s">
+      <c r="H4" s="46"/>
+      <c r="J4" s="46" t="s">
         <v>7</v>
       </c>
-      <c r="K4" s="48"/>
-      <c r="M4" s="48" t="s">
+      <c r="K4" s="46"/>
+      <c r="M4" s="46" t="s">
         <v>8</v>
       </c>
-      <c r="N4" s="48"/>
-      <c r="P4" s="48" t="s">
+      <c r="N4" s="46"/>
+      <c r="P4" s="46" t="s">
         <v>9</v>
       </c>
-      <c r="Q4" s="48"/>
+      <c r="Q4" s="46"/>
       <c r="R4" s="1"/>
-      <c r="S4" s="48" t="s">
+      <c r="S4" s="46" t="s">
         <v>10</v>
       </c>
-      <c r="T4" s="48"/>
+      <c r="T4" s="46"/>
       <c r="U4" s="1"/>
-      <c r="V4" s="48" t="s">
+      <c r="V4" s="46" t="s">
         <v>11</v>
       </c>
-      <c r="W4" s="48"/>
+      <c r="W4" s="46"/>
       <c r="X4" s="1"/>
-      <c r="Y4" s="48" t="s">
+      <c r="Y4" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="Z4" s="48"/>
+      <c r="Z4" s="46"/>
       <c r="AA4" s="1"/>
-      <c r="AB4" s="48" t="s">
+      <c r="AB4" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="AC4" s="48"/>
-      <c r="AE4" s="48" t="s">
+      <c r="AC4" s="46"/>
+      <c r="AE4" s="46" t="s">
         <v>116</v>
       </c>
-      <c r="AF4" s="48"/>
+      <c r="AF4" s="46"/>
       <c r="AG4" s="1"/>
-      <c r="AH4" s="48" t="s">
+      <c r="AH4" s="46" t="s">
         <v>117</v>
       </c>
-      <c r="AI4" s="48"/>
+      <c r="AI4" s="46"/>
       <c r="AJ4" s="1"/>
-      <c r="AK4" s="48" t="s">
+      <c r="AK4" s="46" t="s">
         <v>118</v>
       </c>
-      <c r="AL4" s="48"/>
+      <c r="AL4" s="46"/>
       <c r="AM4" s="1"/>
-      <c r="AN4" s="48" t="s">
+      <c r="AN4" s="46" t="s">
         <v>119</v>
       </c>
-      <c r="AO4" s="48"/>
+      <c r="AO4" s="46"/>
       <c r="AP4" s="1"/>
-      <c r="AQ4" s="48" t="s">
+      <c r="AQ4" s="46" t="s">
         <v>120</v>
       </c>
-      <c r="AR4" s="48"/>
+      <c r="AR4" s="46"/>
     </row>
     <row r="5" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A5" s="41" t="s">
@@ -10506,89 +10527,89 @@
       </c>
     </row>
     <row r="6" spans="1:44" x14ac:dyDescent="0.2">
-      <c r="A6" s="46" t="str">
+      <c r="A6" s="47" t="str">
         <f>_xlfn.XLOOKUP(B5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v>shell</v>
       </c>
-      <c r="B6" s="47"/>
-      <c r="D6" s="46" t="str">
+      <c r="B6" s="48"/>
+      <c r="D6" s="47" t="str">
         <f>_xlfn.XLOOKUP(E5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v>filter</v>
       </c>
-      <c r="E6" s="47"/>
-      <c r="G6" s="46" t="str">
+      <c r="E6" s="48"/>
+      <c r="G6" s="47" t="str">
         <f>_xlfn.XLOOKUP(H5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v>core</v>
       </c>
-      <c r="H6" s="47"/>
-      <c r="J6" s="46" t="str">
+      <c r="H6" s="48"/>
+      <c r="J6" s="47" t="str">
         <f>_xlfn.XLOOKUP(K5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="K6" s="47"/>
-      <c r="M6" s="46" t="str">
+      <c r="K6" s="48"/>
+      <c r="M6" s="47" t="str">
         <f>_xlfn.XLOOKUP(N5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="N6" s="47"/>
-      <c r="P6" s="46" t="str">
+      <c r="N6" s="48"/>
+      <c r="P6" s="47" t="str">
         <f>_xlfn.XLOOKUP(Q5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="Q6" s="47"/>
+      <c r="Q6" s="48"/>
       <c r="R6" s="1"/>
-      <c r="S6" s="46" t="str">
+      <c r="S6" s="47" t="str">
         <f>_xlfn.XLOOKUP(T5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="T6" s="47"/>
+      <c r="T6" s="48"/>
       <c r="U6" s="1"/>
-      <c r="V6" s="46" t="str">
+      <c r="V6" s="47" t="str">
         <f>_xlfn.XLOOKUP(W5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="W6" s="47"/>
+      <c r="W6" s="48"/>
       <c r="X6" s="1"/>
-      <c r="Y6" s="46" t="str">
+      <c r="Y6" s="47" t="str">
         <f>_xlfn.XLOOKUP(Z5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="Z6" s="47"/>
+      <c r="Z6" s="48"/>
       <c r="AA6" s="1"/>
-      <c r="AB6" s="46" t="str">
+      <c r="AB6" s="47" t="str">
         <f>_xlfn.XLOOKUP(AC5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AC6" s="47"/>
-      <c r="AE6" s="46" t="str">
+      <c r="AC6" s="48"/>
+      <c r="AE6" s="47" t="str">
         <f>_xlfn.XLOOKUP(AF5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AF6" s="47"/>
+      <c r="AF6" s="48"/>
       <c r="AG6" s="1"/>
-      <c r="AH6" s="46" t="str">
+      <c r="AH6" s="47" t="str">
         <f>_xlfn.XLOOKUP(AI5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AI6" s="47"/>
+      <c r="AI6" s="48"/>
       <c r="AJ6" s="1"/>
-      <c r="AK6" s="46" t="str">
+      <c r="AK6" s="47" t="str">
         <f>_xlfn.XLOOKUP(AL5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AL6" s="47"/>
+      <c r="AL6" s="48"/>
       <c r="AM6" s="1"/>
-      <c r="AN6" s="46" t="str">
+      <c r="AN6" s="47" t="str">
         <f>_xlfn.XLOOKUP(AO5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AO6" s="47"/>
+      <c r="AO6" s="48"/>
       <c r="AP6" s="1"/>
-      <c r="AQ6" s="46" t="str">
+      <c r="AQ6" s="47" t="str">
         <f>_xlfn.XLOOKUP(AR5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AR6" s="47"/>
+      <c r="AR6" s="48"/>
     </row>
     <row r="7" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
@@ -11548,36 +11569,36 @@
     </row>
   </sheetData>
   <mergeCells count="30">
+    <mergeCell ref="AE6:AF6"/>
+    <mergeCell ref="AH6:AI6"/>
+    <mergeCell ref="AK6:AL6"/>
+    <mergeCell ref="AN6:AO6"/>
+    <mergeCell ref="AQ6:AR6"/>
+    <mergeCell ref="P6:Q6"/>
+    <mergeCell ref="S6:T6"/>
+    <mergeCell ref="V6:W6"/>
+    <mergeCell ref="Y6:Z6"/>
+    <mergeCell ref="AB6:AC6"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="M6:N6"/>
+    <mergeCell ref="AE4:AF4"/>
+    <mergeCell ref="AH4:AI4"/>
+    <mergeCell ref="AK4:AL4"/>
+    <mergeCell ref="AN4:AO4"/>
+    <mergeCell ref="AQ4:AR4"/>
+    <mergeCell ref="P4:Q4"/>
+    <mergeCell ref="S4:T4"/>
+    <mergeCell ref="V4:W4"/>
+    <mergeCell ref="Y4:Z4"/>
+    <mergeCell ref="AB4:AC4"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="D4:E4"/>
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="J4:K4"/>
     <mergeCell ref="M4:N4"/>
-    <mergeCell ref="P4:Q4"/>
-    <mergeCell ref="S4:T4"/>
-    <mergeCell ref="V4:W4"/>
-    <mergeCell ref="Y4:Z4"/>
-    <mergeCell ref="AB4:AC4"/>
-    <mergeCell ref="AE4:AF4"/>
-    <mergeCell ref="AH4:AI4"/>
-    <mergeCell ref="AK4:AL4"/>
-    <mergeCell ref="AN4:AO4"/>
-    <mergeCell ref="AQ4:AR4"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="J6:K6"/>
-    <mergeCell ref="M6:N6"/>
-    <mergeCell ref="P6:Q6"/>
-    <mergeCell ref="S6:T6"/>
-    <mergeCell ref="V6:W6"/>
-    <mergeCell ref="Y6:Z6"/>
-    <mergeCell ref="AB6:AC6"/>
-    <mergeCell ref="AE6:AF6"/>
-    <mergeCell ref="AH6:AI6"/>
-    <mergeCell ref="AK6:AL6"/>
-    <mergeCell ref="AN6:AO6"/>
-    <mergeCell ref="AQ6:AR6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -11935,12 +11956,24 @@
       <c r="N16" s="1"/>
     </row>
   </sheetData>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D5:D12" xr:uid="{06E9E004-FC39-FE49-926A-912F810F5089}">
+  <conditionalFormatting sqref="E3:E42">
+    <cfRule type="expression" dxfId="2" priority="3">
+      <formula>OR($D3="Intercept", $D3="Radius")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F3:G42">
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>OR($D3="Depth",$D3="Radius")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H3:H42">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>OR($D3="Depth",$D3="Intercept")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D3:D52" xr:uid="{8E64B66A-BAAD-494F-8CCA-041428B649F6}">
       <formula1>$J$3:$J$5</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D3:D4" xr:uid="{AEFC92A9-AB07-FF4B-9461-938B9BDCD07D}">
-      <formula1>$J$5:$J$7</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/docs/seep/files/xslope_earth_dam2.xlsx
+++ b/docs/seep/files/xslope_earth_dam2.xlsx
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="158">
   <si>
     <t>X</t>
   </si>
@@ -630,6 +630,37 @@
   </si>
   <si>
     <t>core</t>
+  </si>
+  <si>
+    <t>psi</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="Symbol"/>
+        <charset val="2"/>
+      </rPr>
+      <t>s(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="Aptos Narrow (Body)"/>
+      </rPr>
+      <t>psi</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="Symbol"/>
+        <charset val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -8028,7 +8059,7 @@
         <v>79</v>
       </c>
       <c r="D5" s="35">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
@@ -9488,8 +9519,8 @@
       <c r="I8" s="21" t="s">
         <v>80</v>
       </c>
-      <c r="J8" s="26" t="s">
-        <v>81</v>
+      <c r="J8" s="21" t="s">
+        <v>156</v>
       </c>
       <c r="K8" s="21" t="s">
         <v>88</v>
@@ -9510,7 +9541,7 @@
         <v>82</v>
       </c>
       <c r="Q8" s="23" t="s">
-        <v>83</v>
+        <v>157</v>
       </c>
       <c r="R8" s="25" t="s">
         <v>92</v>
@@ -10272,7 +10303,7 @@
     <mergeCell ref="W7:X7"/>
     <mergeCell ref="R7:V7"/>
   </mergeCells>
-  <conditionalFormatting sqref="E9:F50">
+  <conditionalFormatting sqref="F9:F50">
     <cfRule type="expression" dxfId="9" priority="4">
       <formula>$D9="cp"</formula>
     </cfRule>
@@ -10287,7 +10318,7 @@
       <formula>$D9="cp"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M9:N50">
+  <conditionalFormatting sqref="N9:N50">
     <cfRule type="expression" dxfId="6" priority="7">
       <formula>$D9="cp"</formula>
     </cfRule>
